--- a/reports/content/te/2026-05-15_sync_report.xlsx
+++ b/reports/content/te/2026-05-15_sync_report.xlsx
@@ -462,13 +462,13 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1198</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.0% of prev</t>
+          <t>0.0% of prev</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,402 +695,6 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>after</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>68dfb701dbb984773816642c</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>bb149c1f-e77d-4e68-8a4b-76339b28cb65</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ఎవరి కర్ర ముక్క పెరిగితే  వారే దొంగ అని చెప్పారు.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>68dfb701f18a67f54d96ecc9</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0e81c6f4-b447-4f8f-81a2-54575ef9a351</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ఊరి వారందరికి ఒకోక్క  కర్ర ముక్క ఇచ్చారు.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>68dfb717f18a67f54d96ecdf</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>909f4b29-bad4-41f3-b3b7-531fffde9268</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>రాజు ఉడత గాయనికి  మందు రాసి కట్టు కట్టాడు.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>698039e4db624637288d986e</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>d78bdbd4-63f3-4de2-9be9-e9629bbdc252</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">పాప ఏం చేస్తున్నది? </t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>698039eb90ff9772efaa2a28</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>15461412-d62c-47cf-bde0-f127441dcb68</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">దేవుని మెడలో దీనిని వేద్దాం. </t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>69803a0d90ff9772efaa2a40</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4192f84d-43f0-411d-b9ee-997b9a0a1fa6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">వలలో చిక్కుకున్న జంతువు ఏది? </t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>69803a0ddb624637288d98a8</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>a3d2b20d-e66c-46e3-89ad-93562888cadc</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ఈ ఉత్తరం ఏ రాష్ట్రానికి చెందినది? </t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>69803a0edb624637288d98ac</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0cf2142e-0252-4c18-b9d3-4e19b0876ef1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">వంద' ను ఇలా కూడా అంటారు. </t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>69803a1edb624637288d98be</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>207d2dc6-3878-4b85-9416-745b8e3d9e64</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ఈ పండుగ క్రైస్తవులకు అతిపెద్ద పండుగ. </t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>69c6bae0f3b9dc74c553d4b0</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>accfafce-e261-4d7a-b570-30d05e75a6cb</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">దీనిని పొలంలో వాడుతారు. </t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>69c6bf8bb1e9b1f7b3f0bc8f</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>c8e533a7-c1bb-4889-939c-f5ff4ae8cff5</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>చివరికి పులి  ఒక్కోదాన్ని వేరు చేసి తినేసింది.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>69c6bf8bf3b9dc74c553d4ce</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>a320aa9b-221f-4aae-8c47-1f5b4b5a8e41</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>మీ అవ్వ,  తాతలతో మీరు ఏమేం ముచ్చట్లు చెప్పుతారు.</t>
         </is>
       </c>
     </row>
